--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" s="9">
       <c r="B4" s="3" t="n">
         <v>2</v>
       </c>
@@ -538,45 +538,165 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="5" t="n"/>
+    <row r="5" s="9">
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>CP-008 (prueba automatizada del registro)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - registro</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Después de registrarse no aparecía el mensaje "Tu cuenta fue creada y la sesión está iniciada": la ruta /registro redirigía al perfil antes de que la pantalla enviara el aviso.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 21-09-2026 al crear la prueba automatizada del registro con rol (Vitest); existía desde el Sprint 1. Se corrigió entregando el aviso a través del contexto de sesión, igual que el de inicio de sesión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" s="9">
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CP-019 (revisión visual del asistente)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - entorno de desarrollo</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Después de agregar los catálogos del perfil a shared/reglas.json, el servidor de desarrollo de Vite siguió usando la versión anterior del archivo y los pasos 2 y 3 del asistente quedaban en blanco.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 21-09-2026. No afecta la versión compilada ni las pruebas. Se resuelve reiniciando el frontend y quedó indicado en el README.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" s="9">
+      <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CP-019 (revisión visual del registro)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - registro</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Con la contraseña y su confirmación lado a lado, el texto de ayuda de los campos se cortaba ("Contraseña (mínimo…").</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 21-09-2026 en la captura de computador. Se acortó el texto visible; la etiqueta completa se mantiene para lectores de pantalla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="9">
+      <c r="B8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CP-019 (revisión en celular)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - encabezado</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>En celular el botón "Cerrar sesión" del encabezado se partía en dos líneas.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Interfaz</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 21-09-2026 en la captura a 390 px. En pantallas pequeñas el botón muestra solo el ícono; el texto queda disponible para lectores de pantalla.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="n"/>

--- a/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
+++ b/FASE 2/Evidencias Proyecto/Evidencias de documentación/Plan de Pruebas/Registro_Defectos.xlsx
@@ -698,15 +698,45 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="5" t="n"/>
+    <row r="9" s="9">
+      <c r="B9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CP-022 (prueba manual del cierre de sesión)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Frontend - portada</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Al cerrar sesión se volvía a la portada, pero no aparecía el mensaje "Cerraste sesión correctamente": la portada descartaba el aviso al limpiar un efecto y, en el navegador (modo de desarrollo con StrictMode de React), el aviso se borraba antes de mostrarse.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Funcional</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Corregido</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Detectado el 23-09-2026 al ejecutar CP-022; las pruebas automatizadas no lo reproducían. Se corrigió conservando el aviso al abrir la portada y descartándolo del contexto de sesión; las pruebas del frontend ahora montan la aplicación con StrictMode, igual que main.jsx. CP-022 se volvió a ejecutar y quedó aprobado.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="n"/>
